--- a/claude/09-30-2026-IH35-BUILD-TRACKER.xlsx
+++ b/claude/09-30-2026-IH35-BUILD-TRACKER.xlsx
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2270,10 +2270,10 @@
           <t>K. OWNER ADDENDUM 2 + CODER ORDERS ISSUED 2026-09-30</t>
         </is>
       </c>
-      <c r="B74" s="26" t="n"/>
-      <c r="C74" s="26" t="n"/>
-      <c r="D74" s="26" t="n"/>
-      <c r="E74" s="26" t="n"/>
+      <c r="B74" s="32" t="n"/>
+      <c r="C74" s="32" t="n"/>
+      <c r="D74" s="32" t="n"/>
+      <c r="E74" s="33" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
@@ -2437,9 +2437,237 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>M. FULL SWEEP OF THE OWNER'S MESSAGES — D41..D46 + ORPHAN-GUARD SWEEP</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="n"/>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>D41</t>
+        </is>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>Company settlement PDF — was 500 on every open (42703 column unit_id does not exist)</t>
+        </is>
+      </c>
+      <c r="C82" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D82" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E82" s="27" t="inlineStr">
+        <is>
+          <t>PR #23338. Render 10:21:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>D42</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>Driver settlement PDF — was 500 on every open (25P02, a bare catch left the transaction poisoned)</t>
+        </is>
+      </c>
+      <c r="C83" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D83" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E83" s="27" t="inlineStr">
+        <is>
+          <t>PR #23338. Render 10:37:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>D43</t>
+        </is>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>Invoice PDF — is it ready? Measured live: HTTP 200, renders, one route one template</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>VERIFIED READY</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>Invoice 13593 renders its Line haul row</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>D44</t>
+        </is>
+      </c>
+      <c r="B85" s="29" t="inlineStr">
+        <is>
+          <t>THE PRE-INVOICE MUST BE EXACTLY THE INVOICE — same route, same template already; the gap is the missing invoice_lines</t>
+        </is>
+      </c>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E85" s="29" t="inlineStr">
+        <is>
+          <t>13627 shows Balance due $3,200 over a line table with only Tax $0.00. Blocked on B-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>Lines between SECTIONS inside a box — distinct from row separators; inside every panel there are no section boundaries at all</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D86" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E86" s="31" t="inlineStr">
+        <is>
+          <t>'it just looks too simple, it bothers me'</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>DEPLOY CADENCE — deploys must not depend on someone remembering. Named owner on a stated cadence, or autoDeploy on with the pre-deploy gates carrying the safety</t>
+        </is>
+      </c>
+      <c r="C87" s="31" t="inlineStr">
+        <is>
+          <t>Lead+Owner</t>
+        </is>
+      </c>
+      <c r="D87" s="31" t="inlineStr">
+        <is>
+          <t>OPEN — DECISION</t>
+        </is>
+      </c>
+      <c r="E87" s="31" t="inlineStr">
+        <is>
+          <t>Owner: 'if no one is going to deploy every 5-10 PRs, then I guess I will turn on autodeploy'</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>G-14</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>ORPHAN-GUARD SWEEP — 14 guards that PASSED but ran NOWHERE are now wired (verify-steps 10872..10885)</t>
+        </is>
+      </c>
+      <c r="C88" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>An unwired guard is a fake green</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="inlineStr">
+        <is>
+          <t>G-10</t>
+        </is>
+      </c>
+      <c r="B89" s="29" t="inlineStr">
+        <is>
+          <t>10 orphan guards NOT wired by me on purpose — 8 need a live DATABASE_URL and a baseline their owning seat must set; 2 genuinely FAIL</t>
+        </is>
+      </c>
+      <c r="C89" s="29" t="inlineStr">
+        <is>
+          <t>CC-1/2/3 + Codex</t>
+        </is>
+      </c>
+      <c r="D89" s="29" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E89" s="29" t="inlineStr">
+        <is>
+          <t>A baseline set against CI's empty DB would be a fake green. match-candidates -&gt; CC-2 B-08; geocode -&gt; CC-3 T-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A41:E41"/>

--- a/claude/09-30-2026-IH35-BUILD-TRACKER.xlsx
+++ b/claude/09-30-2026-IH35-BUILD-TRACKER.xlsx
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2443,10 +2443,10 @@
           <t>M. FULL SWEEP OF THE OWNER'S MESSAGES — D41..D46 + ORPHAN-GUARD SWEEP</t>
         </is>
       </c>
-      <c r="B81" s="26" t="n"/>
-      <c r="C81" s="26" t="n"/>
-      <c r="D81" s="26" t="n"/>
-      <c r="E81" s="26" t="n"/>
+      <c r="B81" s="32" t="n"/>
+      <c r="C81" s="32" t="n"/>
+      <c r="D81" s="32" t="n"/>
+      <c r="E81" s="33" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="27" t="inlineStr">
@@ -2664,8 +2664,231 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="25" t="inlineStr">
+        <is>
+          <t>N. G2 ITEM MAP CLOSED FROM THE SIGNED DOCUMENTS + CI UNBLOCKED</t>
+        </is>
+      </c>
+      <c r="B90" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="26" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>G2-1</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>Rule found in the signed settlements: every document separates Additional Pay / Reimbursed Expenses / Deductions. Anything under Reimbursed Expenses is NOT driver pay and must never post to 6890</t>
+        </is>
+      </c>
+      <c r="C91" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D91" s="27" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="E91" s="27" t="inlineStr">
+        <is>
+          <t>Read from Driver_Settlement_5782/5785/5794/5797/5799/5802 text</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>G2-2</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>$18.00 TYSON LUMPER VIAJE PASADO (5782/13540) and $10.00 Warehouse-Lumper Fee Expense COBRO POR ENTRAR A DESCARGA (5785/13538) -&gt; Driver Reimbursement Warehouse-Lumper Fee -&gt; 5310 Lumper Expense</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>Corrected from my earlier FREIGHT-DELI ruling. SALES-OF-SER item has NO expense account — it is revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>G2-3</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>$24.99 LOVES 1ASC H1155LL HEADLIG (5802/13589) and $37.63 LOVES 2AS20WINDSHIELD (5797/13569) -&gt; Road Service-Truck Repair Expense -&gt; 5400 Truck Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="C93" s="27" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="E93" s="27" t="inlineStr">
+        <is>
+          <t>Owner's call confirmed: over-the-road repair, not purchased by us. Precedent 5799/13574 tire 531.26 -&gt; 5500</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="31" t="inlineStr">
+        <is>
+          <t>G2-4</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="inlineStr">
+        <is>
+          <t>$22.14 LOVES 1ASC ''19 PREMIUM (5794/13558) — block arithmetic closed (30.30+22.14+49.32=101.76) so it IS a reimbursed Love's purchase; WHAT it bought is not readable</t>
+        </is>
+      </c>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="D94" s="31" t="inlineStr">
+        <is>
+          <t>OPEN — 1 LINE</t>
+        </is>
+      </c>
+      <c r="E94" s="31" t="inlineStr">
+        <is>
+          <t>Pull the Love's txn by date+amount from fuel.fuel_transactions and banking. Held out of AUTH-159 until named</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>G2-5</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>Catalog verified live — every item needed already exists. CREATE NOTHING</t>
+        </is>
+      </c>
+      <c r="C95" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D95" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>Road Service-Truck Repair/Tire/Trailer/Flatbed/Reefer, OTR-Maintenance-Tools, 4x Driver Reimbursement items</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="27" t="inlineStr">
+        <is>
+          <t>CI-1</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>MIGRATION CHAIN NOW APPLIES END TO END ON A FRESH DATABASE — security-audit-heavy and build-typecheck-heavy no longer fail</t>
+        </is>
+      </c>
+      <c r="C96" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>The two failures that killed every CI run since 2026-09-17 are gone</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>CI-2</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="inlineStr">
+        <is>
+          <t>Remaining red on PR #23338: orphan guards (Codex reports 10 wired, 10/10 pass) and a stale-branch check — rebased and pushed</t>
+        </is>
+      </c>
+      <c r="C97" s="28" t="inlineStr">
+        <is>
+          <t>Lead+Codex</t>
+        </is>
+      </c>
+      <c r="D97" s="28" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="31" t="inlineStr">
+        <is>
+          <t>X-16</t>
+        </is>
+      </c>
+      <c r="B98" s="31" t="inlineStr">
+        <is>
+          <t>A guard requiring a live DATABASE_URL must not run in the LOCAL pre-commit path — it blocks every seat from committing. Move that class into the CI job that has a database</t>
+        </is>
+      </c>
+      <c r="C98" s="31" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="D98" s="31" t="inlineStr">
+        <is>
+          <t>OPEN — P0</t>
+        </is>
+      </c>
+      <c r="E98" s="31" t="inlineStr">
+        <is>
+          <t>Codex blocked on verify-one-load-create-path. This is how work sits in local branches for 10 hours</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
@@ -2673,6 +2896,7 @@
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A90:E90"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>

--- a/claude/09-30-2026-IH35-BUILD-TRACKER.xlsx
+++ b/claude/09-30-2026-IH35-BUILD-TRACKER.xlsx
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2670,10 +2670,10 @@
           <t>N. G2 ITEM MAP CLOSED FROM THE SIGNED DOCUMENTS + CI UNBLOCKED</t>
         </is>
       </c>
-      <c r="B90" s="26" t="n"/>
-      <c r="C90" s="26" t="n"/>
-      <c r="D90" s="26" t="n"/>
-      <c r="E90" s="26" t="n"/>
+      <c r="B90" s="32" t="n"/>
+      <c r="C90" s="32" t="n"/>
+      <c r="D90" s="32" t="n"/>
+      <c r="E90" s="33" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
@@ -2887,8 +2887,438 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="25" t="inlineStr">
+        <is>
+          <t>O. QUICKBOOKS PARITY — the owner's screenshots, 2026-09-30 — ONE systemic pass, lands with C-18</t>
+        </is>
+      </c>
+      <c r="B99" s="26" t="n"/>
+      <c r="C99" s="26" t="n"/>
+      <c r="D99" s="26" t="n"/>
+      <c r="E99" s="26" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="31" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="B100" s="31" t="inlineStr">
+        <is>
+          <t>The QuickBooks CALENDAR / DATE FORMAT was dropped from the ENTIRE APP. QBO shows 9/14/26 and 07/31/2026. One date policy app-wide</t>
+        </is>
+      </c>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D100" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E100" s="31" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="31" t="inlineStr">
+        <is>
+          <t>D48</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="inlineStr">
+        <is>
+          <t>The QuickBooks NUMBER FORMAT and styling were dropped from the ENTIRE APP — alignment, separators, the $5,500.00 shape, right-aligned money</t>
+        </is>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D101" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E101" s="31" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="31" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="B102" s="31" t="inlineStr">
+        <is>
+          <t>Banking Action column — use the QuickBooks text size for text and dates</t>
+        </is>
+      </c>
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D102" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E102" s="31" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>D50</t>
+        </is>
+      </c>
+      <c r="B103" s="31" t="inlineStr">
+        <is>
+          <t>ROW distinction YES, COLUMN lines NO. QuickBooks separates rows and never draws vertical column lines. Exactly the opposite of what we ship</t>
+        </is>
+      </c>
+      <c r="C103" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D103" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>The owner's single clearest statement of the contrast fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="31" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="B104" s="31" t="inlineStr">
+        <is>
+          <t>Column-header text one step LARGER than the row text. Every list in the app</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D104" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E104" s="31" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="31" t="inlineStr">
+        <is>
+          <t>D52</t>
+        </is>
+      </c>
+      <c r="B105" s="31" t="inlineStr">
+        <is>
+          <t>Multi-select / filter control must be LARGER — follow the QuickBooks control sizes</t>
+        </is>
+      </c>
+      <c r="C105" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D105" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E105" s="31" t="inlineStr">
+        <is>
+          <t>Ours measured 131x33 bare input, border 0px</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="31" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="B106" s="31" t="inlineStr">
+        <is>
+          <t>Add the QuickBooks PRINTER and EXPORT icons to list toolbars, in the QuickBooks position</t>
+        </is>
+      </c>
+      <c r="C106" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D106" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E106" s="31" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="31" t="inlineStr">
+        <is>
+          <t>D54</t>
+        </is>
+      </c>
+      <c r="B107" s="31" t="inlineStr">
+        <is>
+          <t>Banking actions = the QuickBooks set: Add / Match / Record transfer, rendered as QuickBooks renders them</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D107" s="31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E107" s="31" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="25" t="inlineStr">
+        <is>
+          <t>P. LEAD RULINGS — 2026-09-30</t>
+        </is>
+      </c>
+      <c r="B108" s="26" t="n"/>
+      <c r="C108" s="26" t="n"/>
+      <c r="D108" s="26" t="n"/>
+      <c r="E108" s="26" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="29" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="B109" s="29" t="inlineStr">
+        <is>
+          <t>PRODUCTION NEAR-MISS — a rehearsal script reused a stale connection string and called voidDocument against PRODUCTION on a real factoring advance. Nothing persisted by LUCK, not by control</t>
+        </is>
+      </c>
+      <c r="C109" s="29" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="D109" s="29" t="inlineStr">
+        <is>
+          <t>P0 — GUARD REQUIRED</t>
+        </is>
+      </c>
+      <c r="E109" s="29" t="inlineStr">
+        <is>
+          <t>Ship assertNotProduction() + a guard failing any ops/rehearsal script that writes without it. Ahead of A-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="29" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="B110" s="29" t="inlineStr">
+        <is>
+          <t>REINSTATE IS HEADER-ONLY — restores the header, not the GL. Exact mirror of the void bug: one shows voided while money is live, the other shows live while money is reversed</t>
+        </is>
+      </c>
+      <c r="C110" s="29" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="D110" s="29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E110" s="29" t="inlineStr">
+        <is>
+          <t>Step 1 refuse when GL cannot be re-posted. Step 2 re-post family by family with a TB round-trip proof each</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>VOID ENGINE FACTORING HOLE — executeVoidCancel('factoring_advance') never reversed the GL, header-only, on a false comment. FIXED + merged PR #23353</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E111" s="27" t="inlineStr">
+        <is>
+          <t>Found while proving B-01. Worth more than the $17,057.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>204 database-required guard candidates — route by BEHAVIOUR: STATIC stays local; ISOLATED runs on CI's loopback DB; LIVE-DATA runs in CI on the read-only prod credential with the owning seat's baseline</t>
+        </is>
+      </c>
+      <c r="C112" s="27" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>RULED</t>
+        </is>
+      </c>
+      <c r="E112" s="27" t="inlineStr">
+        <is>
+          <t>Never a baseline from an empty database</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>G5 CLOSED — driver 51, company 51. Root cause: 3 settlements closed without the company-settlement side effect firing. AUTH-167, PRs #23350/#23351</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E113" s="27" t="inlineStr">
+        <is>
+          <t>Off the close gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>$17,057.44 double-booked factoring REVERSED — TB delta exact, account 1090 $17,867.98 -&gt; $16,162.34</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="D114" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E114" s="27" t="inlineStr">
+        <is>
+          <t>AUTH-165 CONSUMED, reversal-JE register in the board</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>DEP-1</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>PR #23338 MERGED f2e965f838 and DEPLOYED. Company Settlements register 200, company settlement PDF 200, driver settlement PDF 200, invoice PDF 200</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E115" s="27" t="inlineStr">
+        <is>
+          <t>All four were 500 one hour earlier</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>BUS-1</t>
+        </is>
+      </c>
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>Coder bus RESTARTED — NOW-*.md and OUTBOX-*.md rewritten for CC-1, CC-2, CC-3, CODEX, CURSOR</t>
+        </is>
+      </c>
+      <c r="C116" s="27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D116" s="27" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E116" s="27" t="inlineStr">
+        <is>
+          <t>One entry per job id; an entry without its job id is not a report</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
@@ -2897,11 +3327,13 @@
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A108:E108"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A67:E67"/>
   </mergeCells>
